--- a/data/WP17/WP17_sachgebiete_GRÜNE.xlsx
+++ b/data/WP17/WP17_sachgebiete_GRÜNE.xlsx
@@ -71,10 +71,10 @@
     <t xml:space="preserve">Landwirtschaftliche Betriebe</t>
   </si>
   <si>
+    <t xml:space="preserve">Schadstoffe, Immissionen, Emissionen</t>
+  </si>
+  <si>
     <t xml:space="preserve">Verkehrswegebau</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Schadstoffe, Immissionen, Emissionen</t>
   </si>
   <si>
     <t xml:space="preserve">Erneuerbare Energien</t>
@@ -1029,10 +1029,10 @@
         <v>64</v>
       </c>
       <c r="D16" t="n">
-        <v>32.375</v>
+        <v>33.046875</v>
       </c>
       <c r="E16" t="n">
-        <v>47</v>
+        <v>44</v>
       </c>
     </row>
     <row r="17">
@@ -1043,13 +1043,13 @@
         <v>17</v>
       </c>
       <c r="C17" t="n">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D17" t="n">
-        <v>32.9206349206349</v>
+        <v>32.375</v>
       </c>
       <c r="E17" t="n">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="18">
@@ -1182,7 +1182,7 @@
         <v>37</v>
       </c>
       <c r="D25" t="n">
-        <v>31.5405405405405</v>
+        <v>31.4594594594595</v>
       </c>
       <c r="E25" t="n">
         <v>21</v>
@@ -1981,7 +1981,7 @@
         <v>6</v>
       </c>
       <c r="D72" t="n">
-        <v>25.1666666666667</v>
+        <v>29.6666666666667</v>
       </c>
       <c r="E72" t="n">
         <v>3</v>
@@ -3326,13 +3326,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D8DE364E-FF5D-43A3-A724-85FF2A62F521}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{DF54513F-DC08-4AF7-A8F5-C36C68A7DD2A}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9BA81E39-C644-4E5C-9077-86155AB72298}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{63E580A8-67DB-4EE9-9187-BE7F4ECE1F93}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{7B134E68-A14F-4893-9141-A95712F90ADA}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{35526B3C-833D-4776-A67C-0816CE93377B}"/>
 </file>
--- a/data/WP17/WP17_sachgebiete_GRÜNE.xlsx
+++ b/data/WP17/WP17_sachgebiete_GRÜNE.xlsx
@@ -446,7 +446,7 @@
         <v>33.1691176470588</v>
       </c>
       <c r="E2" t="n">
-        <v>96</v>
+        <v>100</v>
       </c>
     </row>
     <row r="3">
@@ -463,7 +463,7 @@
         <v>32.4414414414414</v>
       </c>
       <c r="E3" t="n">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="4">
@@ -480,7 +480,7 @@
         <v>30.6454545454545</v>
       </c>
       <c r="E4" t="n">
-        <v>68</v>
+        <v>89</v>
       </c>
     </row>
     <row r="5">
@@ -497,7 +497,7 @@
         <v>32.8673469387755</v>
       </c>
       <c r="E5" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6">
@@ -514,7 +514,7 @@
         <v>32.1237113402062</v>
       </c>
       <c r="E6" t="n">
-        <v>54</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7">
@@ -531,7 +531,7 @@
         <v>35.5670103092784</v>
       </c>
       <c r="E7" t="n">
-        <v>77</v>
+        <v>79</v>
       </c>
     </row>
     <row r="8">
@@ -565,7 +565,7 @@
         <v>28.1481481481481</v>
       </c>
       <c r="E9" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10">
@@ -582,7 +582,7 @@
         <v>32.6</v>
       </c>
       <c r="E10" t="n">
-        <v>51</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11">
@@ -616,7 +616,7 @@
         <v>20.8219178082192</v>
       </c>
       <c r="E12" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="13">
@@ -633,7 +633,7 @@
         <v>32.2285714285714</v>
       </c>
       <c r="E13" t="n">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="14">
@@ -650,7 +650,7 @@
         <v>31.2898550724638</v>
       </c>
       <c r="E14" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="15">
@@ -667,7 +667,7 @@
         <v>24.9076923076923</v>
       </c>
       <c r="E15" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="16">
@@ -684,7 +684,7 @@
         <v>32.921875</v>
       </c>
       <c r="E16" t="n">
-        <v>43</v>
+        <v>49</v>
       </c>
     </row>
     <row r="17">
@@ -701,7 +701,7 @@
         <v>32.09375</v>
       </c>
       <c r="E17" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
     </row>
     <row r="18">
@@ -718,7 +718,7 @@
         <v>35.1538461538462</v>
       </c>
       <c r="E18" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="19">
@@ -735,7 +735,7 @@
         <v>30.75</v>
       </c>
       <c r="E19" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="20">
@@ -752,7 +752,7 @@
         <v>26.6888888888889</v>
       </c>
       <c r="E20" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
@@ -769,7 +769,7 @@
         <v>27.7380952380952</v>
       </c>
       <c r="E21" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -1006,13 +1006,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A53A9BE7-7A76-4354-AB5A-20004C2BAAFE}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{449C9853-F31E-4EB0-A5E5-110E3B352C29}"/>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1B20C5AE-8CD9-4525-BEFB-FAD16E376143}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{14CE5FFF-8E1A-444B-A388-CBF682AC339C}"/>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{A3002BDA-3BE1-4321-A87A-F4F761DD738A}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{081A592A-F43B-4FC4-A85D-946238878D81}"/>
 </file>